--- a/PFP-C/Input data and Generated Schedule/47.xlsx
+++ b/PFP-C/Input data and Generated Schedule/47.xlsx
@@ -32594,7 +32594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32619,7 +32619,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>objective all vehicle travel individually</t>
+          <t>objective_all_vehicle_travel_individually</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -32629,7 +32629,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>objective LLA</t>
+          <t>objective_LLA</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -32639,11 +32639,131 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>objective lb</t>
+          <t>objective_lb</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>43.245</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_10</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_10</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_15</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_15</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_20</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_25</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_30</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_30</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -43598,7 +43718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43634,25 +43754,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Saving_time_(minute)</t>
+          <t>Saving_time(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time(%)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
@@ -43685,18 +43800,15 @@
         <v>1.485714285714287</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>302.43993993994</v>
       </c>
       <c r="I2" t="n">
-        <v>302.43993993994</v>
+        <v>0.7807807807807814</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7807807807807814</v>
-      </c>
-      <c r="K2" t="n">
         <v>0.2581606056844981</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -43729,18 +43841,15 @@
         <v>9.999999999999984</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>359.4587087087088</v>
       </c>
       <c r="I3" t="n">
-        <v>359.4587087087088</v>
+        <v>6.021021021021011</v>
       </c>
       <c r="J3" t="n">
-        <v>6.021021021021011</v>
-      </c>
-      <c r="K3" t="n">
         <v>1.675024383927282</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43773,18 +43882,15 @@
         <v>1.570247933884296</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>302.7304804804805</v>
       </c>
       <c r="I4" t="n">
-        <v>302.7304804804805</v>
+        <v>0.8558558558558549</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8558558558558549</v>
-      </c>
-      <c r="K4" t="n">
         <v>0.2827121519106626</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43817,18 +43923,15 @@
         <v>7.02479338842975</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>343.5713213213214</v>
       </c>
       <c r="I5" t="n">
-        <v>343.5713213213214</v>
+        <v>3.828828828828827</v>
       </c>
       <c r="J5" t="n">
-        <v>3.828828828828827</v>
-      </c>
-      <c r="K5" t="n">
         <v>1.114420381219175</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -43861,18 +43964,15 @@
         <v>8.62842892768079</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>352.8521021021021</v>
       </c>
       <c r="I6" t="n">
-        <v>352.8521021021021</v>
+        <v>5.195195195195189</v>
       </c>
       <c r="J6" t="n">
-        <v>5.195195195195189</v>
-      </c>
-      <c r="K6" t="n">
         <v>1.472343558177782</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43905,18 +44005,15 @@
         <v>8.766233766233771</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>399.9534534534534</v>
       </c>
       <c r="I7" t="n">
-        <v>399.9534534534534</v>
+        <v>6.081081081081084</v>
       </c>
       <c r="J7" t="n">
-        <v>6.081081081081084</v>
-      </c>
-      <c r="K7" t="n">
         <v>1.520447199186092</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -43949,18 +44046,15 @@
         <v>8.900000000000006</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>432.9579579579579</v>
       </c>
       <c r="I8" t="n">
-        <v>432.9579579579579</v>
+        <v>6.681681681681686</v>
       </c>
       <c r="J8" t="n">
-        <v>6.681681681681686</v>
-      </c>
-      <c r="K8" t="n">
         <v>1.54326339517947</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43993,18 +44087,15 @@
         <v>2.244094488188974</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>211.5210210210211</v>
       </c>
       <c r="I9" t="n">
-        <v>211.5210210210211</v>
+        <v>0.8558558558558549</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8558558558558549</v>
-      </c>
-      <c r="K9" t="n">
         <v>0.4046197639008179</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -44037,18 +44128,15 @@
         <v>3.289473684210535</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>406.5645645645645</v>
       </c>
       <c r="I10" t="n">
-        <v>406.5645645645645</v>
+        <v>2.252252252252257</v>
       </c>
       <c r="J10" t="n">
-        <v>2.252252252252257</v>
-      </c>
-      <c r="K10" t="n">
         <v>0.553971607108565</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -44081,18 +44169,15 @@
         <v>8.722358722358733</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>349.8445945945946</v>
       </c>
       <c r="I11" t="n">
-        <v>349.8445945945946</v>
+        <v>5.330330330330336</v>
       </c>
       <c r="J11" t="n">
-        <v>5.330330330330336</v>
-      </c>
-      <c r="K11" t="n">
         <v>1.523628037331035</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -44125,18 +44210,15 @@
         <v>6.772334293948123</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>293.7334834834835</v>
       </c>
       <c r="I12" t="n">
-        <v>293.7334834834835</v>
+        <v>3.528528528528526</v>
       </c>
       <c r="J12" t="n">
-        <v>3.528528528528526</v>
-      </c>
-      <c r="K12" t="n">
         <v>1.201268744265219</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -44169,18 +44251,15 @@
         <v>7.543859649122814</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>398.156156156156</v>
       </c>
       <c r="I13" t="n">
-        <v>398.156156156156</v>
+        <v>5.16516516516517</v>
       </c>
       <c r="J13" t="n">
-        <v>5.16516516516517</v>
-      </c>
-      <c r="K13" t="n">
         <v>1.297271205104613</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -44213,18 +44292,15 @@
         <v>2.639593908629444</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>168.9211711711712</v>
       </c>
       <c r="I14" t="n">
-        <v>168.9211711711712</v>
+        <v>0.7807807807807814</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7807807807807814</v>
-      </c>
-      <c r="K14" t="n">
         <v>0.4622160593414313</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -44257,18 +44333,15 @@
         <v>6.601307189542482</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>257.7282282282282</v>
       </c>
       <c r="I15" t="n">
-        <v>257.7282282282282</v>
+        <v>3.033033033033032</v>
       </c>
       <c r="J15" t="n">
-        <v>3.033033033033032</v>
-      </c>
-      <c r="K15" t="n">
         <v>1.176833850868352</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -44301,18 +44374,15 @@
         <v>7.768924302788838</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>221.7334834834835</v>
       </c>
       <c r="I16" t="n">
-        <v>221.7334834834835</v>
+        <v>2.927927927927925</v>
       </c>
       <c r="J16" t="n">
-        <v>2.927927927927925</v>
-      </c>
-      <c r="K16" t="n">
         <v>1.320471713125826</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -44345,18 +44415,15 @@
         <v>7.000000000000011</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>444.6696696696696</v>
       </c>
       <c r="I17" t="n">
-        <v>444.6696696696696</v>
+        <v>5.255255255255263</v>
       </c>
       <c r="J17" t="n">
-        <v>5.255255255255263</v>
-      </c>
-      <c r="K17" t="n">
         <v>1.18183353030559</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -44389,18 +44456,15 @@
         <v>1.850649350649348</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>271.2402402402403</v>
       </c>
       <c r="I18" t="n">
-        <v>271.2402402402403</v>
+        <v>0.8558558558558549</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8558558558558549</v>
-      </c>
-      <c r="K18" t="n">
         <v>0.3155342493052706</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -44433,18 +44497,15 @@
         <v>1.779935275080897</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>293.1614114114113</v>
       </c>
       <c r="I19" t="n">
-        <v>293.1614114114113</v>
+        <v>0.8258258258258214</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8258258258258214</v>
-      </c>
-      <c r="K19" t="n">
         <v>0.281696633213056</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -44477,18 +44538,15 @@
         <v>5.227272727272728</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>251.1201201201201</v>
       </c>
       <c r="I20" t="n">
-        <v>251.1201201201201</v>
+        <v>2.417417417417417</v>
       </c>
       <c r="J20" t="n">
-        <v>2.417417417417417</v>
-      </c>
-      <c r="K20" t="n">
         <v>0.9626538153378855</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -44521,18 +44579,15 @@
         <v>9.999999999999988</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>322.2500000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>322.2500000000001</v>
+        <v>5.450450450450443</v>
       </c>
       <c r="J21" t="n">
-        <v>5.450450450450443</v>
-      </c>
-      <c r="K21" t="n">
         <v>1.691373297269338</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -44565,18 +44620,15 @@
         <v>3.668831168831169</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>254.1231231231232</v>
       </c>
       <c r="I22" t="n">
-        <v>254.1231231231232</v>
+        <v>1.696696696696696</v>
       </c>
       <c r="J22" t="n">
-        <v>1.696696696696696</v>
-      </c>
-      <c r="K22" t="n">
         <v>0.6676671826808313</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -44609,18 +44661,15 @@
         <v>1.40049140049141</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>343.237987987988</v>
       </c>
       <c r="I23" t="n">
-        <v>343.237987987988</v>
+        <v>0.8558558558558615</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8558558558558615</v>
-      </c>
-      <c r="K23" t="n">
         <v>0.2493476496796774</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -44653,18 +44702,15 @@
         <v>8.155339805825236</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>274.5427927927928</v>
       </c>
       <c r="I24" t="n">
-        <v>274.5427927927928</v>
+        <v>3.78378378378378</v>
       </c>
       <c r="J24" t="n">
-        <v>3.78378378378378</v>
-      </c>
-      <c r="K24" t="n">
         <v>1.378212753390156</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -44697,18 +44743,15 @@
         <v>8.429752066115679</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>328.5563063063063</v>
       </c>
       <c r="I25" t="n">
-        <v>328.5563063063063</v>
+        <v>4.594594594594581</v>
       </c>
       <c r="J25" t="n">
-        <v>4.594594594594581</v>
-      </c>
-      <c r="K25" t="n">
         <v>1.398419237861511</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -44741,18 +44784,15 @@
         <v>2.039473684210526</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>408.0660660660661</v>
       </c>
       <c r="I26" t="n">
-        <v>408.0660660660661</v>
+        <v>1.396396396396396</v>
       </c>
       <c r="J26" t="n">
-        <v>1.396396396396396</v>
-      </c>
-      <c r="K26" t="n">
         <v>0.3421986076564177</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -44769,7 +44809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44795,20 +44835,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time_(minute)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Saving_time(%)</t>
         </is>
@@ -44841,9 +44876,6 @@
       <c r="H2" t="n">
         <v>25</v>
       </c>
-      <c r="I2" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -44864,15 +44896,12 @@
         <v>5.660364400768392</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>319.7253753753754</v>
       </c>
       <c r="G3" t="n">
-        <v>319.7253753753754</v>
+        <v>3.218018018018017</v>
       </c>
       <c r="H3" t="n">
-        <v>3.218018018018017</v>
-      </c>
-      <c r="I3" t="n">
         <v>0.9710235845212221</v>
       </c>
     </row>
@@ -44895,15 +44924,12 @@
         <v>3.090405292069673</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>72.00186875505791</v>
       </c>
       <c r="G4" t="n">
-        <v>72.00186875505791</v>
+        <v>2.033868261118962</v>
       </c>
       <c r="H4" t="n">
-        <v>2.033868261118962</v>
-      </c>
-      <c r="I4" t="n">
         <v>0.5238750549065301</v>
       </c>
     </row>
@@ -44926,15 +44952,12 @@
         <v>1.40049140049141</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>168.9211711711712</v>
       </c>
       <c r="G5" t="n">
-        <v>168.9211711711712</v>
+        <v>0.7807807807807814</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7807807807807814</v>
-      </c>
-      <c r="I5" t="n">
         <v>0.2493476496796774</v>
       </c>
     </row>
@@ -44957,15 +44980,12 @@
         <v>2.244094488188974</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>271.2402402402403</v>
       </c>
       <c r="G6" t="n">
-        <v>271.2402402402403</v>
+        <v>0.8558558558558615</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8558558558558615</v>
-      </c>
-      <c r="I6" t="n">
         <v>0.4046197639008179</v>
       </c>
     </row>
@@ -44988,15 +45008,12 @@
         <v>6.772334293948123</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>322.2500000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>322.2500000000001</v>
+        <v>3.033033033033032</v>
       </c>
       <c r="H7" t="n">
-        <v>3.033033033033032</v>
-      </c>
-      <c r="I7" t="n">
         <v>1.176833850868352</v>
       </c>
     </row>
@@ -45019,15 +45036,12 @@
         <v>8.429752066115679</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>359.4587087087088</v>
       </c>
       <c r="G8" t="n">
-        <v>359.4587087087088</v>
+        <v>5.195195195195189</v>
       </c>
       <c r="H8" t="n">
-        <v>5.195195195195189</v>
-      </c>
-      <c r="I8" t="n">
         <v>1.398419237861511</v>
       </c>
     </row>
@@ -45050,15 +45064,12 @@
         <v>9.999999999999988</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>444.6696696696696</v>
       </c>
       <c r="G9" t="n">
-        <v>444.6696696696696</v>
+        <v>6.681681681681686</v>
       </c>
       <c r="H9" t="n">
-        <v>6.681681681681686</v>
-      </c>
-      <c r="I9" t="n">
         <v>1.691373297269338</v>
       </c>
     </row>
